--- a/docs/downloads/经营分_津河省区__滨海片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__滨海片区_2026-10-18.xlsx
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>-27</v>
+        <v>-42</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>30</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>30</v>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -907,13 +907,13 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
         <v>20</v>
@@ -1211,29 +1211,29 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7289447316170213391</t>
+          <t>7438848647481821247</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>维也纳智好酒店石化园区喜荣街店</t>
+          <t>白玉兰商务酒店（天津大港油田步行街店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>维也纳智好酒店石化园区喜荣街店</t>
+          <t>白玉兰酒店(天津大港油田步行街店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>87</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1299,17 +1299,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6691413193794799627</t>
+          <t>7289447316170213391</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津于家堡金融中心店）</t>
+          <t>维也纳智好酒店石化园区喜荣街店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津于家堡金融中心店)</t>
+          <t>维也纳智好酒店石化园区喜荣街店</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1321,7 +1321,7 @@
         <v>87</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1387,17 +1387,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601149668816603150</t>
+          <t>6691413193794799627</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津极地海洋公园滨海高铁站店</t>
+          <t>维也纳酒店（天津于家堡金融中心店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津极地海洋公园滨海高铁站店)</t>
+          <t>维也纳酒店(天津于家堡金融中心店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1429,7 +1429,7 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1441,7 +1441,7 @@
         <v>30</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="n">
         <v>20</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1827,33 +1827,33 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6678104788686686221</t>
+          <t>7556654794754557979</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津滨海开发区第三大街MSD店）</t>
+          <t>维也纳酒店（天津滨海新区大港油田步行街店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津滨海开发区第三大街MSD店)</t>
+          <t>维也纳酒店(天津滨海新区大港油田步行街店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1863,25 +1863,25 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T15" t="n">
         <v>20</v>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7438848647481821247</t>
+          <t>6678104788686686221</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（天津大港油田步行街店）</t>
+          <t>喆啡酒店（天津滨海开发区第三大街MSD店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>白玉兰酒店(天津大港油田步行街店)</t>
+          <t>喆啡酒店(天津滨海开发区第三大街MSD店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1937,11 +1937,11 @@
         <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1951,13 +1951,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -1969,7 +1969,7 @@
         <v>30</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T16" t="n">
         <v>20</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2179,17 +2179,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6848943961499879439</t>
+          <t>6601149668816603150</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津中新生态城国家海博馆店)</t>
+          <t>麗枫酒店·天津极地海洋公园滨海高铁站店</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津中新生态城店)</t>
+          <t>麗枫酒店(天津极地海洋公园滨海高铁站店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2198,14 +2198,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2215,25 +2215,25 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T19" t="n">
         <v>20</v>
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7556654794754557979</t>
+          <t>6848943961499879439</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津滨海新区大港油田步行街店）</t>
+          <t>凯里亚德酒店(天津中新生态城国家海博馆店)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津滨海新区大港油田步行街店)</t>
+          <t>凯里亚德酒店(天津中新生态城店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2289,11 +2289,11 @@
         <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2303,13 +2303,13 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3059,33 +3059,33 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6704924329206876168</t>
+          <t>6601141776730294279</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（天津于家堡金融中心店）</t>
+          <t>锦江之星天津滨海新区海洋高新区酒店</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津于家堡金融中心店)</t>
+          <t>锦江之星(天津海洋高新区店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3101,7 +3101,7 @@
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6823655529584379912</t>
+          <t>6704924329206876168</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津滨海新区塘沽地铁站店）</t>
+          <t>凯里亚德酒店（天津于家堡金融中心店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津滨海新区塘沽地铁站店)</t>
+          <t>凯里亚德酒店(天津于家堡金融中心店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3169,11 +3169,11 @@
         <v>110</v>
       </c>
       <c r="I30" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3189,13 +3189,13 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3235,33 +3235,33 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6601148547385559053</t>
+          <t>6823655529584379912</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>锦江之星品尚天津塘沽地铁站中心北路酒店</t>
+          <t>维也纳国际酒店（天津滨海新区塘沽地铁站店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>锦江之星品尚(天津塘沽地铁站中心北路酒店)</t>
+          <t>维也纳国际酒店(天津滨海新区塘沽地铁站店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>110</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3277,13 +3277,13 @@
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6601141776730294279</t>
+          <t>6601148547385559053</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>锦江之星天津滨海新区海洋高新区酒店</t>
+          <t>锦江之星品尚天津塘沽地铁站中心北路酒店</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>锦江之星(天津海洋高新区店)</t>
+          <t>锦江之星品尚(天津塘沽地铁站中心北路酒店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3365,13 +3365,13 @@
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
